--- a/data/B24_department_schedules_midterms/Elektrik-Elektronik Mühendisliği.xlsx
+++ b/data/B24_department_schedules_midterms/Elektrik-Elektronik Mühendisliği.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e402f802124af4b/Masaüstü/Projects/Campus-Scheduling/data/department_schedules_midterms/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e402f802124af4b/Masaüstü/Projects/Campus-Scheduling/data/B24_department_schedules_midterms/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="13_ncr:1_{A962BC1D-70B3-40C6-A964-1ED82DFC0C99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3ED9E185-30AD-4AE3-BF51-F7C855235D43}"/>
+  <xr:revisionPtr revIDLastSave="83" documentId="13_ncr:1_{A962BC1D-70B3-40C6-A964-1ED82DFC0C99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{06FDD1FC-5056-4F28-90DF-62E7B57183C2}"/>
   <bookViews>
-    <workbookView xWindow="-17640" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20760" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="113">
   <si>
     <t>Year:</t>
   </si>
@@ -356,6 +356,9 @@
   </si>
   <si>
     <t>D202,C208</t>
+  </si>
+  <si>
+    <t>timeslots</t>
   </si>
 </sst>
 </file>
@@ -436,7 +439,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -453,11 +456,18 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="11">
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -535,20 +545,17 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{79ACEB52-309D-4060-8C3C-DC7C9F3B92A5}" name="Table1" displayName="Table1" ref="A1:F39" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6">
-  <autoFilter ref="A1:F39" xr:uid="{79ACEB52-309D-4060-8C3C-DC7C9F3B92A5}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{5EAD184A-303E-4A69-9475-B700029CFC48}" name="Year:" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{BF2E3D95-414C-4E99-9D7B-C5F21434DC8D}" name="Course ID" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{F3390BF1-A074-49AF-A024-F1A1EE7E9D1A}" name="Date" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{967E76CD-124C-44DB-BB57-34781E73C3A6}" name="Rooms" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{96FEEE3B-B858-437C-BB9A-4310C172E207}" name="Course Name" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{69024B88-989D-4300-A191-6BFAD7A5C7EB}" name="Rooms Used" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{79ACEB52-309D-4060-8C3C-DC7C9F3B92A5}" name="Table1" displayName="Table1" ref="A1:G39" totalsRowShown="0" headerRowDxfId="10" dataDxfId="8" headerRowBorderDxfId="9" tableBorderDxfId="7">
+  <autoFilter ref="A1:G39" xr:uid="{79ACEB52-309D-4060-8C3C-DC7C9F3B92A5}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{5EAD184A-303E-4A69-9475-B700029CFC48}" name="Year:" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{BF2E3D95-414C-4E99-9D7B-C5F21434DC8D}" name="Course ID" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{F3390BF1-A074-49AF-A024-F1A1EE7E9D1A}" name="Date" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{967E76CD-124C-44DB-BB57-34781E73C3A6}" name="Rooms" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{96FEEE3B-B858-437C-BB9A-4310C172E207}" name="Course Name" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{69024B88-989D-4300-A191-6BFAD7A5C7EB}" name="Rooms Used" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{B1725069-9B69-4125-ACA1-04CC8571E8DF}" name="timeslots" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium22" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -841,7 +848,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="10.9296875" customWidth="1"/>
@@ -849,7 +856,7 @@
     <col min="6" max="6" width="38.265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -868,8 +875,11 @@
       <c r="F1" s="1" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G1" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -888,8 +898,12 @@
       <c r="F2" s="2" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G2" s="7">
+        <v>2</v>
+      </c>
+      <c r="I2" s="6"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -908,8 +922,12 @@
       <c r="F3" s="2" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G3" s="7">
+        <v>5</v>
+      </c>
+      <c r="I3" s="6"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -928,8 +946,12 @@
       <c r="F4" s="2" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G4" s="7">
+        <v>2</v>
+      </c>
+      <c r="I4" s="6"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" s="2">
         <v>1</v>
       </c>
@@ -948,8 +970,12 @@
       <c r="F5" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G5" s="7">
+        <v>5</v>
+      </c>
+      <c r="I5" s="6"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" s="2">
         <v>1</v>
       </c>
@@ -968,8 +994,11 @@
       <c r="F6" s="2" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G6" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" s="3">
         <v>2</v>
       </c>
@@ -988,8 +1017,12 @@
       <c r="F7" s="3" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G7" s="7">
+        <v>5</v>
+      </c>
+      <c r="I7" s="6"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" s="3">
         <v>2</v>
       </c>
@@ -1008,8 +1041,12 @@
       <c r="F8" s="3" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G8" s="7">
+        <v>2</v>
+      </c>
+      <c r="I8" s="6"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9" s="3">
         <v>2</v>
       </c>
@@ -1028,8 +1065,12 @@
       <c r="F9" s="3" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G9" s="7">
+        <v>7</v>
+      </c>
+      <c r="I9" s="6"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" s="3">
         <v>2</v>
       </c>
@@ -1048,8 +1089,12 @@
       <c r="F10" s="3" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G10" s="7">
+        <v>2</v>
+      </c>
+      <c r="I10" s="6"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11" s="3">
         <v>2</v>
       </c>
@@ -1068,8 +1113,11 @@
       <c r="F11" s="3" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G11" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A12" s="3">
         <v>2</v>
       </c>
@@ -1088,8 +1136,11 @@
       <c r="F12" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G12" s="7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A13" s="3">
         <v>2</v>
       </c>
@@ -1108,8 +1159,11 @@
       <c r="F13" s="3" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G13" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A14" s="4">
         <v>3</v>
       </c>
@@ -1128,8 +1182,11 @@
       <c r="F14" s="4" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G14" s="7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A15" s="4">
         <v>3</v>
       </c>
@@ -1148,8 +1205,11 @@
       <c r="F15" s="4" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G15" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A16" s="4">
         <v>3</v>
       </c>
@@ -1168,8 +1228,11 @@
       <c r="F16" s="4" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G16" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" s="4">
         <v>3</v>
       </c>
@@ -1188,8 +1251,11 @@
       <c r="F17" s="4" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G17" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" s="4">
         <v>3</v>
       </c>
@@ -1208,8 +1274,11 @@
       <c r="F18" s="4" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G18" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" s="4">
         <v>3</v>
       </c>
@@ -1228,8 +1297,11 @@
       <c r="F19" s="4" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G19" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" s="4">
         <v>3</v>
       </c>
@@ -1248,8 +1320,11 @@
       <c r="F20" s="4" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G20" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" s="4">
         <v>3</v>
       </c>
@@ -1268,8 +1343,11 @@
       <c r="F21" s="4" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G21" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" s="4">
         <v>3</v>
       </c>
@@ -1288,8 +1366,11 @@
       <c r="F22" s="4" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G22" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" s="4">
         <v>3</v>
       </c>
@@ -1308,8 +1389,11 @@
       <c r="F23" s="4" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G23" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" s="5">
         <v>4</v>
       </c>
@@ -1328,8 +1412,11 @@
       <c r="F24" s="5" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G24" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" s="5">
         <v>4</v>
       </c>
@@ -1348,8 +1435,11 @@
       <c r="F25" s="5" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G25" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" s="5">
         <v>4</v>
       </c>
@@ -1368,8 +1458,11 @@
       <c r="F26" s="5" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G26" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27" s="5">
         <v>4</v>
       </c>
@@ -1388,8 +1481,11 @@
       <c r="F27" s="5" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G27" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28" s="5">
         <v>4</v>
       </c>
@@ -1408,8 +1504,11 @@
       <c r="F28" s="5" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G28" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29" s="5">
         <v>4</v>
       </c>
@@ -1428,8 +1527,11 @@
       <c r="F29" s="5" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G29" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30" s="5">
         <v>4</v>
       </c>
@@ -1448,8 +1550,11 @@
       <c r="F30" s="5" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G30" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31" s="5">
         <v>4</v>
       </c>
@@ -1468,8 +1573,11 @@
       <c r="F31" s="5" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G31" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32" s="5">
         <v>4</v>
       </c>
@@ -1488,8 +1596,11 @@
       <c r="F32" s="5" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G32" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A33" s="5">
         <v>4</v>
       </c>
@@ -1508,8 +1619,11 @@
       <c r="F33" s="5" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G33" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A34" s="5">
         <v>4</v>
       </c>
@@ -1528,8 +1642,11 @@
       <c r="F34" s="5" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G34" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A35" s="5">
         <v>4</v>
       </c>
@@ -1548,8 +1665,11 @@
       <c r="F35" s="5" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G35" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A36" s="5">
         <v>4</v>
       </c>
@@ -1568,8 +1688,11 @@
       <c r="F36" s="5" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G36" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A37" s="5">
         <v>4</v>
       </c>
@@ -1588,8 +1711,11 @@
       <c r="F37" s="5" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G37" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A38" s="5">
         <v>4</v>
       </c>
@@ -1608,8 +1734,11 @@
       <c r="F38" s="5" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G38" s="7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A39" s="5">
         <v>4</v>
       </c>
@@ -1627,6 +1756,9 @@
       </c>
       <c r="F39" s="5" t="s">
         <v>111</v>
+      </c>
+      <c r="G39" s="7">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/data/B24_department_schedules_midterms/Elektrik-Elektronik Mühendisliği.xlsx
+++ b/data/B24_department_schedules_midterms/Elektrik-Elektronik Mühendisliği.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e402f802124af4b/Masaüstü/Projects/Campus-Scheduling/data/B24_department_schedules_midterms/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="83" documentId="13_ncr:1_{A962BC1D-70B3-40C6-A964-1ED82DFC0C99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{06FDD1FC-5056-4F28-90DF-62E7B57183C2}"/>
+  <xr:revisionPtr revIDLastSave="84" documentId="13_ncr:1_{A962BC1D-70B3-40C6-A964-1ED82DFC0C99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B40869F3-6BC8-4CD1-9FC5-0B3E987478BE}"/>
   <bookViews>
     <workbookView xWindow="20760" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -543,6 +543,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -995,7 +999,7 @@
         <v>86</v>
       </c>
       <c r="G6" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">
